--- a/BWI/bestwine_output/bestwine_Macedonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Macedonia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5861,6 +5861,95 @@
       <c r="Z49" s="3" t="inlineStr"/>
       <c r="AA49" s="3" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Wine.mk</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Wine.mk</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>9525</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Macedonia</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Skopje</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Qyteti i Shkupit, Komuna e Gazi Babës</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Kamnik Bb</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.mk</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>support@wine.mk</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>+389 2 252 1786</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>4030996424929</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine.mk_store/</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
